--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-xx-pig-slurry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E32DDCA-7C20-435E-91E8-4CAC4178E092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E8E74C-5405-416F-AE72-959282AE7AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,8 +35,64 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}</author>
+    <author>tc={41F19D6E-E99D-4BC4-9CF8-03971525C4BB}</author>
+    <author>tc={34F919C0-E213-42BB-B018-7CF158825172}</author>
+    <author>tc={BD837BDB-798F-46E2-9B1E-095AD2C34354}</author>
+    <author>tc={74A47A3C-9B82-4D0E-8273-A61F47053664}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    General observations:
+- first cycle was changed from std - Jar 6 was put after 2 to test the picarro early (std most sure emission source). As this one provided a realistic meausrement it was propoed initial low concentrations of 1 and 2 stemmed from initial adsorption in the system
+- slurry had visibly better penetration in the packed soil samples</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{41F19D6E-E99D-4BC4-9CF8-03971525C4BB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Whether the notes on the samples were aligned with the sheet</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="2" shapeId="0" xr:uid="{34F919C0-E213-42BB-B018-7CF158825172}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not exact time - need to go into file and find valve 1 for exact</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="3" shapeId="0" xr:uid="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The red plastic piece of this one was not replaced with glass</t>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="4" shapeId="0" xr:uid="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Didn’t write this one - avg of other backgrounds- both sample and bypass</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>Valve code</t>
   </si>
@@ -99,6 +155,15 @@
   </si>
   <si>
     <t>F Untr</t>
+  </si>
+  <si>
+    <t>Chek</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>02/19-2026</t>
   </si>
 </sst>
 </file>
@@ -108,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +181,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,6 +207,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -149,13 +226,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -171,6 +249,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Mikael Løvig Larsen" id="{41FB0084-A38E-4055-BCE6-FE39473376DA}" userId="S::au705323@uni.au.dk::501b5c6e-34b9-41fc-bcf2-dc0650cde639" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,26 +518,47 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-22T14:05:30.51" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}">
+    <text>General observations:
+- first cycle was changed from std - Jar 6 was put after 2 to test the picarro early (std most sure emission source). As this one provided a realistic meausrement it was propoed initial low concentrations of 1 and 2 stemmed from initial adsorption in the system
+- slurry had visibly better penetration in the packed soil samples</text>
+  </threadedComment>
+  <threadedComment ref="O1" dT="2026-02-19T08:43:58.04" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{41F19D6E-E99D-4BC4-9CF8-03971525C4BB}">
+    <text>Whether the notes on the samples were aligned with the sheet</text>
+  </threadedComment>
+  <threadedComment ref="G2" dT="2026-02-22T14:00:45.12" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{34F919C0-E213-42BB-B018-7CF158825172}">
+    <text>Not exact time - need to go into file and find valve 1 for exact</text>
+  </threadedComment>
+  <threadedComment ref="F3" dT="2026-02-22T13:48:32.41" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
+    <text>The red plastic piece of this one was not replaced with glass</text>
+  </threadedComment>
+  <threadedComment ref="I14" dT="2026-02-22T13:53:01.18" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
+    <text>Didn’t write this one - avg of other backgrounds- both sample and bypass</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,35 +571,38 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -507,12 +615,26 @@
       <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="2"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>2.0609999999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.4375</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J2">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -525,8 +647,18 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>2.0310000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0.223</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -539,9 +671,18 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>2.0103</v>
+      </c>
+      <c r="I4">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -554,8 +695,18 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="J5">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -568,8 +719,18 @@
       <c r="D6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="I6">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J6">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -582,8 +743,17 @@
       <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="J7">
+        <v>0.79400000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -596,9 +766,18 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>2.1720000000000002</v>
+      </c>
+      <c r="I8">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="O8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -611,9 +790,19 @@
       <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>2.0609999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="O9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -626,9 +815,18 @@
       <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F10" s="3">
+        <v>2.0259999999999998</v>
+      </c>
+      <c r="I10">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J10">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -641,9 +839,18 @@
       <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F11" s="3">
+        <v>2.0259999999999998</v>
+      </c>
+      <c r="I11">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -656,9 +863,18 @@
       <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F12" s="3">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I12">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -671,8 +887,14 @@
       <c r="D13" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.95099999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -685,10 +907,21 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F14" s="3">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I14">
+        <f>AVERAGE(I7,I25,I20)</f>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="J14" s="3">
+        <f>AVERAGE(J7,J20,J25)</f>
+        <v>0.76833333333333342</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -701,9 +934,18 @@
       <c r="D15" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F15" s="3">
+        <v>2.052</v>
+      </c>
+      <c r="I15">
+        <v>0.224</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -716,9 +958,18 @@
       <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="I16">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -731,9 +982,18 @@
       <c r="D17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="3">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="I17">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -746,9 +1006,18 @@
       <c r="D18" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="3">
+        <v>2.0449999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -761,8 +1030,17 @@
       <c r="D19" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>16</v>
       </c>
@@ -775,9 +1053,18 @@
       <c r="D20" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="3">
+        <v>2.0339999999999998</v>
+      </c>
+      <c r="I20">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O20" s="6"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
@@ -790,9 +1077,18 @@
       <c r="D21" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="3">
+        <v>2.044</v>
+      </c>
+      <c r="I21">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -805,9 +1101,18 @@
       <c r="D22" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="3">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="I22">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="O22" s="6"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -820,9 +1125,18 @@
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="3">
+        <v>2.0550000000000002</v>
+      </c>
+      <c r="I23">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="O23" s="6"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -835,9 +1149,18 @@
       <c r="D24" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="3">
+        <v>2.024</v>
+      </c>
+      <c r="I24">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="O24" s="6"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -850,8 +1173,15 @@
       <c r="D25" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="I25">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.755</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E8E74C-5405-416F-AE72-959282AE7AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42011724-95C2-4AFA-A1A1-4E9C554DFDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,6 +41,7 @@
     <author>tc={8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}</author>
     <author>tc={41F19D6E-E99D-4BC4-9CF8-03971525C4BB}</author>
     <author>tc={34F919C0-E213-42BB-B018-7CF158825172}</author>
+    <author>tc={9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}</author>
     <author>tc={BD837BDB-798F-46E2-9B1E-095AD2C34354}</author>
     <author>tc={74A47A3C-9B82-4D0E-8273-A61F47053664}</author>
   </authors>
@@ -71,7 +72,15 @@
     Not exact time - need to go into file and find valve 1 for exact</t>
       </text>
     </comment>
-    <comment ref="F3" authorId="3" shapeId="0" xr:uid="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
+    <comment ref="M2" authorId="3" shapeId="0" xr:uid="{9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Approx time when starting to measure the valves, not the end of the last cycle</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="4" shapeId="0" xr:uid="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -79,7 +88,7 @@
     The red plastic piece of this one was not replaced with glass</t>
       </text>
     </comment>
-    <comment ref="I14" authorId="4" shapeId="0" xr:uid="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
+    <comment ref="I14" authorId="5" shapeId="0" xr:uid="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
   <si>
     <t>Valve code</t>
   </si>
@@ -164,6 +173,9 @@
   </si>
   <si>
     <t>02/19-2026</t>
+  </si>
+  <si>
+    <t>02/25-2026</t>
   </si>
 </sst>
 </file>
@@ -531,6 +543,9 @@
   <threadedComment ref="G2" dT="2026-02-22T14:00:45.12" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{34F919C0-E213-42BB-B018-7CF158825172}">
     <text>Not exact time - need to go into file and find valve 1 for exact</text>
   </threadedComment>
+  <threadedComment ref="M2" dT="2026-02-26T10:23:52.59" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}">
+    <text>Approx time when starting to measure the valves, not the end of the last cycle</text>
+  </threadedComment>
   <threadedComment ref="F3" dT="2026-02-22T13:48:32.41" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
     <text>The red plastic piece of this one was not replaced with glass</text>
   </threadedComment>
@@ -552,10 +567,11 @@
     <col min="6" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -586,10 +602,10 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M1" t="s">
@@ -630,8 +646,18 @@
       <c r="J2">
         <v>0.94899999999999995</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="2"/>
+      <c r="K2" s="3">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.11874999999999999</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -656,6 +682,12 @@
       <c r="J3" s="3">
         <v>0.95</v>
       </c>
+      <c r="K3" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.96599999999999997</v>
+      </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -680,6 +712,12 @@
       <c r="J4" s="3">
         <v>0.94699999999999995</v>
       </c>
+      <c r="K4" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.97499999999999998</v>
+      </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -704,6 +742,12 @@
       <c r="J5">
         <v>0.94699999999999995</v>
       </c>
+      <c r="K5" s="3">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -728,6 +772,12 @@
       <c r="J6">
         <v>0.94499999999999995</v>
       </c>
+      <c r="K6" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.97299999999999998</v>
+      </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -752,6 +802,12 @@
       <c r="J7">
         <v>0.79400000000000004</v>
       </c>
+      <c r="K7" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.79500000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -775,6 +831,12 @@
       <c r="J8" s="3">
         <v>0.94699999999999995</v>
       </c>
+      <c r="K8" s="3">
+        <v>0.216</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.97</v>
+      </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -799,7 +861,12 @@
       <c r="J9" s="3">
         <v>0.95</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>0.217</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.97</v>
+      </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -824,6 +891,12 @@
       <c r="J10">
         <v>0.94699999999999995</v>
       </c>
+      <c r="K10" s="3">
+        <v>0.217</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.97</v>
+      </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -848,6 +921,12 @@
       <c r="J11" s="3">
         <v>0.95</v>
       </c>
+      <c r="K11" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.96799999999999997</v>
+      </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -872,6 +951,12 @@
       <c r="J12" s="3">
         <v>0.95099999999999996</v>
       </c>
+      <c r="K12" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.96499999999999997</v>
+      </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -893,6 +978,12 @@
       <c r="J13" s="3">
         <v>0.95099999999999996</v>
       </c>
+      <c r="K13" s="3">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.79600000000000004</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -918,7 +1009,12 @@
         <f>AVERAGE(J7,J20,J25)</f>
         <v>0.76833333333333342</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>0.223</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.95399999999999996</v>
+      </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -943,6 +1039,12 @@
       <c r="J15" s="3">
         <v>0.95099999999999996</v>
       </c>
+      <c r="K15" s="3">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -967,6 +1069,12 @@
       <c r="J16" s="3">
         <v>0.95099999999999996</v>
       </c>
+      <c r="K16" s="3">
+        <v>0.192</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.99399999999999999</v>
+      </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -991,6 +1099,12 @@
       <c r="J17" s="3">
         <v>0.94899999999999995</v>
       </c>
+      <c r="K17" s="3">
+        <v>0.215</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.97199999999999998</v>
+      </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -1015,6 +1129,12 @@
       <c r="J18" s="3">
         <v>0.94599999999999995</v>
       </c>
+      <c r="K18" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.96699999999999997</v>
+      </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1039,6 +1159,12 @@
       <c r="J19" s="3">
         <v>0.95</v>
       </c>
+      <c r="K19" s="3">
+        <v>0.752</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.439</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -1062,6 +1188,12 @@
       <c r="J20" s="3">
         <v>0.75600000000000001</v>
       </c>
+      <c r="K20" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.97399999999999998</v>
+      </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -1086,6 +1218,12 @@
       <c r="J21" s="3">
         <v>0.95</v>
       </c>
+      <c r="K21" s="3">
+        <v>0.224</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0.96499999999999997</v>
+      </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1110,6 +1248,12 @@
       <c r="J22" s="3">
         <v>0.94899999999999995</v>
       </c>
+      <c r="K22" s="3">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0.97899999999999998</v>
+      </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1134,6 +1278,12 @@
       <c r="J23" s="3">
         <v>0.95</v>
       </c>
+      <c r="K23" s="3">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0.96099999999999997</v>
+      </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -1158,6 +1308,12 @@
       <c r="J24" s="3">
         <v>0.94799999999999995</v>
       </c>
+      <c r="K24" s="3">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.97599999999999998</v>
+      </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -1178,6 +1334,12 @@
       </c>
       <c r="J25" s="3">
         <v>0.755</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.441</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0.753</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42011724-95C2-4AFA-A1A1-4E9C554DFDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD52175A-78D5-4077-83C7-B6EEC2796379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,11 +39,13 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}</author>
+    <author>tc={C98AD125-B9D1-4DC6-B29A-EE666E06C597}</author>
     <author>tc={41F19D6E-E99D-4BC4-9CF8-03971525C4BB}</author>
     <author>tc={34F919C0-E213-42BB-B018-7CF158825172}</author>
     <author>tc={9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}</author>
     <author>tc={BD837BDB-798F-46E2-9B1E-095AD2C34354}</author>
     <author>tc={74A47A3C-9B82-4D0E-8273-A61F47053664}</author>
+    <author>tc={5FABE69D-7D9C-487D-8D7F-4B0424AC8BC4}</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{8DC1FA48-6C73-43B8-B575-39BC1BCA9B35}">
@@ -56,7 +58,15 @@
 - slurry had visibly better penetration in the packed soil samples</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{41F19D6E-E99D-4BC4-9CF8-03971525C4BB}">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{C98AD125-B9D1-4DC6-B29A-EE666E06C597}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Standard liters per minute</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="2" shapeId="0" xr:uid="{41F19D6E-E99D-4BC4-9CF8-03971525C4BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -64,7 +74,7 @@
     Whether the notes on the samples were aligned with the sheet</t>
       </text>
     </comment>
-    <comment ref="G2" authorId="2" shapeId="0" xr:uid="{34F919C0-E213-42BB-B018-7CF158825172}">
+    <comment ref="G2" authorId="3" shapeId="0" xr:uid="{34F919C0-E213-42BB-B018-7CF158825172}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -72,7 +82,7 @@
     Not exact time - need to go into file and find valve 1 for exact</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="3" shapeId="0" xr:uid="{9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}">
+    <comment ref="M2" authorId="4" shapeId="0" xr:uid="{9EFC68A0-E0CF-42A9-8A43-AB7809A53DCD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +90,7 @@
     Approx time when starting to measure the valves, not the end of the last cycle</t>
       </text>
     </comment>
-    <comment ref="F3" authorId="4" shapeId="0" xr:uid="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
+    <comment ref="F3" authorId="5" shapeId="0" xr:uid="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -88,7 +98,7 @@
     The red plastic piece of this one was not replaced with glass</t>
       </text>
     </comment>
-    <comment ref="I14" authorId="5" shapeId="0" xr:uid="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
+    <comment ref="I13" authorId="6" shapeId="0" xr:uid="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -96,12 +106,20 @@
     Didn’t write this one - avg of other backgrounds- both sample and bypass</t>
       </text>
     </comment>
+    <comment ref="J13" authorId="7" shapeId="0" xr:uid="{5FABE69D-7D9C-487D-8D7F-4B0424AC8BC4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The yellow columns were originally switched, then later corrected as the mistake was noticed by consulting paper-written notes from the day of the experiment</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
   <si>
     <t>Valve code</t>
   </si>
@@ -124,18 +142,6 @@
     <t>startdate</t>
   </si>
   <si>
-    <t>Q sample start [L/min]</t>
-  </si>
-  <si>
-    <t>Q Bypass start [L/min]</t>
-  </si>
-  <si>
-    <t>Q sample end [mL/min]</t>
-  </si>
-  <si>
-    <t>Q  Bypass end [L/min]</t>
-  </si>
-  <si>
     <t>endtime Piccarro</t>
   </si>
   <si>
@@ -176,6 +182,27 @@
   </si>
   <si>
     <t>02/25-2026</t>
+  </si>
+  <si>
+    <t>Q tot start [L/min]</t>
+  </si>
+  <si>
+    <t>Q sample start [SL/min]</t>
+  </si>
+  <si>
+    <t>Q Bypass start [SL/min]</t>
+  </si>
+  <si>
+    <t>Q sample end [SL/min]</t>
+  </si>
+  <si>
+    <t>Q  Bypass end [SL/min]</t>
+  </si>
+  <si>
+    <t>Q tot end [SL/min]</t>
+  </si>
+  <si>
+    <t>Q mean [SL/min]</t>
   </si>
 </sst>
 </file>
@@ -200,7 +227,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +252,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -238,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -246,6 +279,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,6 +572,9 @@
 - first cycle was changed from std - Jar 6 was put after 2 to test the picarro early (std most sure emission source). As this one provided a realistic meausrement it was propoed initial low concentrations of 1 and 2 stemmed from initial adsorption in the system
 - slurry had visibly better penetration in the packed soil samples</text>
   </threadedComment>
+  <threadedComment ref="I1" dT="2026-03-12T10:45:59.68" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{C98AD125-B9D1-4DC6-B29A-EE666E06C597}">
+    <text>Standard liters per minute</text>
+  </threadedComment>
   <threadedComment ref="O1" dT="2026-02-19T08:43:58.04" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{41F19D6E-E99D-4BC4-9CF8-03971525C4BB}">
     <text>Whether the notes on the samples were aligned with the sheet</text>
   </threadedComment>
@@ -549,32 +587,39 @@
   <threadedComment ref="F3" dT="2026-02-22T13:48:32.41" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{BD837BDB-798F-46E2-9B1E-095AD2C34354}">
     <text>The red plastic piece of this one was not replaced with glass</text>
   </threadedComment>
-  <threadedComment ref="I14" dT="2026-02-22T13:53:01.18" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
+  <threadedComment ref="I13" dT="2026-02-22T13:53:01.18" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{74A47A3C-9B82-4D0E-8273-A61F47053664}">
     <text>Didn’t write this one - avg of other backgrounds- both sample and bypass</text>
+  </threadedComment>
+  <threadedComment ref="J13" dT="2026-03-12T10:44:35.82" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{5FABE69D-7D9C-487D-8D7F-4B0424AC8BC4}">
+    <text>The yellow columns were originally switched, then later corrected as the mistake was noticed by consulting paper-written notes from the day of the experiment</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -597,28 +642,37 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
       <c r="O1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -629,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>2.0609999999999999</v>
@@ -638,7 +692,7 @@
         <v>0.4375</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>0.22500000000000001</v>
@@ -656,11 +710,23 @@
         <v>0.11874999999999999</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>SUM(I2,J2)</f>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="R2" s="3">
+        <f>SUM(K2,L2)</f>
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="S2" s="8">
+        <f>(Q2+R2)/2</f>
+        <v>1.1789999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -671,7 +737,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>2.0310000000000001</v>
@@ -689,8 +755,20 @@
         <v>0.96599999999999997</v>
       </c>
       <c r="O3" s="6"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f>SUM(I3,J3)</f>
+        <v>1.173</v>
+      </c>
+      <c r="R3" s="3">
+        <f>SUM(K3,L3)</f>
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="S3" s="8">
+        <f t="shared" ref="S3:S25" si="0">(Q3+R3)/2</f>
+        <v>1.1795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -701,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>2.0103</v>
@@ -719,8 +797,20 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="O4" s="6"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f>SUM(I4,J4)</f>
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="R4" s="3">
+        <f>SUM(K4,L4)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S4" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -731,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>2.0150000000000001</v>
@@ -749,8 +839,20 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f>SUM(I5,J5)</f>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="R5" s="3">
+        <f>SUM(K5,L5)</f>
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -761,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>2.1030000000000002</v>
@@ -779,8 +881,20 @@
         <v>0.97299999999999998</v>
       </c>
       <c r="O6" s="6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f>SUM(I6,J6)</f>
+        <v>1.171</v>
+      </c>
+      <c r="R6" s="3">
+        <f>SUM(K6,L6)</f>
+        <v>1.204</v>
+      </c>
+      <c r="S6" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -788,13 +902,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
         <v>18</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
       </c>
       <c r="I7">
         <v>0.38700000000000001</v>
@@ -808,8 +922,20 @@
       <c r="L7" s="3">
         <v>0.79500000000000004</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f>SUM(I7,J7)</f>
+        <v>1.181</v>
+      </c>
+      <c r="R7" s="3">
+        <f>SUM(K7,L7)</f>
+        <v>1.1910000000000001</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1859999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -820,7 +946,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>2.1720000000000002</v>
@@ -838,8 +964,20 @@
         <v>0.97</v>
       </c>
       <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f>SUM(I8,J8)</f>
+        <v>1.173</v>
+      </c>
+      <c r="R8" s="3">
+        <f>SUM(K8,L8)</f>
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="S8" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1795</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -850,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F9">
         <v>2.0609999999999999</v>
@@ -868,8 +1006,20 @@
         <v>0.97</v>
       </c>
       <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f>SUM(I9,J9)</f>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R9" s="3">
+        <f>SUM(K9,L9)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1815</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -880,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3">
         <v>2.0259999999999998</v>
@@ -898,8 +1048,20 @@
         <v>0.97</v>
       </c>
       <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f>SUM(I10,J10)</f>
+        <v>1.173</v>
+      </c>
+      <c r="R10" s="3">
+        <f>SUM(K10,L10)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1800000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -910,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3">
         <v>2.0259999999999998</v>
@@ -928,8 +1090,20 @@
         <v>0.96799999999999997</v>
       </c>
       <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f>SUM(I11,J11)</f>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R11" s="3">
+        <f>SUM(K11,L11)</f>
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" si="0"/>
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -940,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F12" s="3">
         <v>2.0499999999999998</v>
@@ -958,8 +1132,20 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <f>SUM(I12,J12)</f>
+        <v>1.177</v>
+      </c>
+      <c r="R12" s="3">
+        <f>SUM(K12,L12)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1819999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -967,25 +1153,39 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0.95099999999999996</v>
-      </c>
-      <c r="K13" s="3">
+        <v>14</v>
+      </c>
+      <c r="I13" s="7">
+        <f>AVERAGE(I7,I25,I19)</f>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="J13" s="8">
+        <f>AVERAGE(J7,J19,J25)</f>
+        <v>0.76833333333333342</v>
+      </c>
+      <c r="K13" s="8">
         <v>0.39700000000000002</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="8">
         <v>0.79600000000000004</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q13" s="3">
+        <f>SUM(I13,J13)</f>
+        <v>1.1813333333333333</v>
+      </c>
+      <c r="R13" s="3">
+        <f>SUM(K13,L13)</f>
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="S13" s="8">
+        <f>(Q13+R13)/2</f>
+        <v>1.1871666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -996,28 +1196,38 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I14">
-        <f>AVERAGE(I7,I25,I20)</f>
-        <v>0.41299999999999998</v>
-      </c>
-      <c r="J14" s="3">
-        <f>AVERAGE(J7,J20,J25)</f>
-        <v>0.76833333333333342</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="7">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="K14" s="8">
         <v>0.223</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="8">
         <v>0.95399999999999996</v>
       </c>
       <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q14">
+        <f>SUM(I14,J14)</f>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R14" s="3">
+        <f>SUM(K14,L14)</f>
+        <v>1.177</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1764999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -1028,7 +1238,7 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3">
         <v>2.052</v>
@@ -1046,8 +1256,20 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="O15" s="6"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q15">
+        <f>SUM(I15,J15)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R15" s="3">
+        <f>SUM(K15,L15)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S15" s="8">
+        <f t="shared" si="0"/>
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1058,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F16" s="3">
         <v>2.12</v>
@@ -1076,8 +1298,20 @@
         <v>0.99399999999999999</v>
       </c>
       <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q16">
+        <f>SUM(I16,J16)</f>
+        <v>1.177</v>
+      </c>
+      <c r="R16" s="3">
+        <f>SUM(K16,L16)</f>
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="S16" s="8">
+        <f>(Q16+R16)/2</f>
+        <v>1.1815</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1088,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F17" s="3">
         <v>2.0459999999999998</v>
@@ -1106,8 +1340,20 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="O17" s="6"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q17">
+        <f>SUM(I17,J17)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R17" s="3">
+        <f>SUM(K17,L17)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S17" s="8">
+        <f>(Q17+R17)/2</f>
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1118,7 +1364,7 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3">
         <v>2.0449999999999999</v>
@@ -1136,8 +1382,20 @@
         <v>0.96699999999999997</v>
       </c>
       <c r="O18" s="6"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <f>SUM(I18,J18)</f>
+        <v>1.171</v>
+      </c>
+      <c r="R18" s="3">
+        <f>SUM(K18,L18)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" si="0"/>
+        <v>1.179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1145,28 +1403,40 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19">
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="I19" s="7">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0.439</v>
+      </c>
+      <c r="L19" s="8">
         <v>0.752</v>
       </c>
-      <c r="L19" s="3">
-        <v>0.439</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q19">
+        <f>SUM(I19,J19)</f>
+        <v>1.1819999999999999</v>
+      </c>
+      <c r="R19" s="3">
+        <f>SUM(K19,L19)</f>
+        <v>1.1910000000000001</v>
+      </c>
+      <c r="S19" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1865000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1177,26 +1447,38 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F20" s="3">
         <v>2.0339999999999998</v>
       </c>
-      <c r="I20">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0.75600000000000001</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="I20" s="7">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="K20" s="8">
         <v>0.21199999999999999</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="8">
         <v>0.97399999999999998</v>
       </c>
       <c r="O20" s="6"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q20">
+        <f>SUM(I20,J20)</f>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R20" s="3">
+        <f>SUM(K20,L20)</f>
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="S20" s="3">
+        <f t="shared" si="0"/>
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1207,7 +1489,7 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F21" s="3">
         <v>2.044</v>
@@ -1225,8 +1507,20 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="O21" s="6"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q21">
+        <f>SUM(I21,J21)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R21" s="3">
+        <f>SUM(K21,L21)</f>
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="S21" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1819999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1237,7 +1531,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>2.0139999999999998</v>
@@ -1255,8 +1549,20 @@
         <v>0.97899999999999998</v>
       </c>
       <c r="O22" s="6"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <f>SUM(I22,J22)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R22" s="3">
+        <f>SUM(K22,L22)</f>
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="S22" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -1267,7 +1573,7 @@
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3">
         <v>2.0550000000000002</v>
@@ -1285,8 +1591,20 @@
         <v>0.96099999999999997</v>
       </c>
       <c r="O23" s="6"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q23">
+        <f>SUM(I23,J23)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R23" s="3">
+        <f>SUM(K23,L23)</f>
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="S23" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1815</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1297,7 +1615,7 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3">
         <v>2.024</v>
@@ -1315,8 +1633,20 @@
         <v>0.97599999999999998</v>
       </c>
       <c r="O24" s="6"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q24">
+        <f>SUM(I24,J24)</f>
+        <v>1.175</v>
+      </c>
+      <c r="R24" s="3">
+        <f>SUM(K24,L24)</f>
+        <v>1.1870000000000001</v>
+      </c>
+      <c r="S24" s="3">
+        <f t="shared" si="0"/>
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1324,10 +1654,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I25">
         <v>0.42599999999999999</v>
@@ -1340,6 +1670,18 @@
       </c>
       <c r="L25" s="3">
         <v>0.753</v>
+      </c>
+      <c r="Q25">
+        <f>SUM(I25,J25)</f>
+        <v>1.181</v>
+      </c>
+      <c r="R25" s="3">
+        <f>SUM(K25,L25)</f>
+        <v>1.194</v>
+      </c>
+      <c r="S25" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1875</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry-picarro.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD52175A-78D5-4077-83C7-B6EEC2796379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B047DCAD-07B4-4261-A91C-EC8ABE119FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
+    <sheet name="Startimes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -118,8 +119,28 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0512BD21-7929-41DA-9007-7AFE0C102E88}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0512BD21-7929-41DA-9007-7AFE0C102E88}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    General observations:
+- first cycle was changed from std - Jar 6 was put after 2 to test the picarro early (std most sure emission source). As this one provided a realistic meausrement it was propoed initial low concentrations of 1 and 2 stemmed from initial adsorption in the system
+- slurry had visibly better penetration in the packed soil samples</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>Valve code</t>
   </si>
@@ -203,16 +224,60 @@
   </si>
   <si>
     <t>Q mean [SL/min]</t>
+  </si>
+  <si>
+    <t>Starttime</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>t [h]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,9 +286,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -271,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -281,6 +364,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,6 +689,16 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-22T14:05:30.51" personId="{41FB0084-A38E-4055-BCE6-FE39473376DA}" id="{0512BD21-7929-41DA-9007-7AFE0C102E88}">
+    <text>General observations:
+- first cycle was changed from std - Jar 6 was put after 2 to test the picarro early (std most sure emission source). As this one provided a realistic meausrement it was propoed initial low concentrations of 1 and 2 stemmed from initial adsorption in the system
+- slurry had visibly better penetration in the packed soil samples</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S25"/>
@@ -605,7 +708,8 @@
     <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
@@ -632,7 +736,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -662,6 +766,7 @@
       <c r="O1" t="s">
         <v>17</v>
       </c>
+      <c r="P1" s="12"/>
       <c r="Q1" t="s">
         <v>21</v>
       </c>
@@ -685,7 +790,7 @@
       <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>2.0609999999999999</v>
       </c>
       <c r="G2" s="1">
@@ -713,15 +818,16 @@
         <v>20</v>
       </c>
       <c r="O2" s="6"/>
+      <c r="P2" s="12"/>
       <c r="Q2">
-        <f>SUM(I2,J2)</f>
+        <f t="shared" ref="Q2:Q25" si="0">SUM(I2,J2)</f>
         <v>1.1739999999999999</v>
       </c>
       <c r="R2" s="3">
-        <f>SUM(K2,L2)</f>
+        <f t="shared" ref="R2:R25" si="1">SUM(K2,L2)</f>
         <v>1.1839999999999999</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="9">
         <f>(Q2+R2)/2</f>
         <v>1.1789999999999998</v>
       </c>
@@ -739,7 +845,7 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>2.0310000000000001</v>
       </c>
       <c r="I3">
@@ -755,16 +861,17 @@
         <v>0.96599999999999997</v>
       </c>
       <c r="O3" s="6"/>
+      <c r="P3" s="12"/>
       <c r="Q3">
-        <f>SUM(I3,J3)</f>
+        <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
       <c r="R3" s="3">
-        <f>SUM(K3,L3)</f>
+        <f t="shared" si="1"/>
         <v>1.1859999999999999</v>
       </c>
-      <c r="S3" s="8">
-        <f t="shared" ref="S3:S25" si="0">(Q3+R3)/2</f>
+      <c r="S3" s="9">
+        <f t="shared" ref="S3:S25" si="2">(Q3+R3)/2</f>
         <v>1.1795</v>
       </c>
     </row>
@@ -781,7 +888,7 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>2.0103</v>
       </c>
       <c r="I4">
@@ -797,16 +904,17 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="O4" s="6"/>
+      <c r="P4" s="12"/>
       <c r="Q4">
-        <f>SUM(I4,J4)</f>
+        <f t="shared" si="0"/>
         <v>1.1719999999999999</v>
       </c>
       <c r="R4" s="3">
-        <f>SUM(K4,L4)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S4" s="8">
-        <f t="shared" si="0"/>
+      <c r="S4" s="9">
+        <f t="shared" si="2"/>
         <v>1.1795</v>
       </c>
     </row>
@@ -823,7 +931,7 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>2.0150000000000001</v>
       </c>
       <c r="I5">
@@ -839,16 +947,17 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="O5" s="6"/>
+      <c r="P5" s="12"/>
       <c r="Q5">
-        <f>SUM(I5,J5)</f>
+        <f t="shared" si="0"/>
         <v>1.1739999999999999</v>
       </c>
       <c r="R5" s="3">
-        <f>SUM(K5,L5)</f>
+        <f t="shared" si="1"/>
         <v>1.1890000000000001</v>
       </c>
-      <c r="S5" s="8">
-        <f t="shared" si="0"/>
+      <c r="S5" s="9">
+        <f t="shared" si="2"/>
         <v>1.1815</v>
       </c>
     </row>
@@ -865,7 +974,7 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>2.1030000000000002</v>
       </c>
       <c r="I6">
@@ -881,16 +990,17 @@
         <v>0.97299999999999998</v>
       </c>
       <c r="O6" s="6"/>
+      <c r="P6" s="12"/>
       <c r="Q6">
-        <f>SUM(I6,J6)</f>
+        <f t="shared" si="0"/>
         <v>1.171</v>
       </c>
       <c r="R6" s="3">
-        <f>SUM(K6,L6)</f>
+        <f t="shared" si="1"/>
         <v>1.204</v>
       </c>
-      <c r="S6" s="8">
-        <f t="shared" si="0"/>
+      <c r="S6" s="9">
+        <f t="shared" si="2"/>
         <v>1.1875</v>
       </c>
     </row>
@@ -907,31 +1017,35 @@
       <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I7">
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12">
         <v>0.38700000000000001</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="12">
         <v>0.79400000000000004</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="13">
         <v>0.39600000000000002</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="13">
         <v>0.79500000000000004</v>
       </c>
-      <c r="Q7">
-        <f>SUM(I7,J7)</f>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="4">
+        <f t="shared" si="0"/>
         <v>1.181</v>
       </c>
-      <c r="R7" s="3">
-        <f>SUM(K7,L7)</f>
+      <c r="R7" s="10">
+        <f t="shared" si="1"/>
         <v>1.1910000000000001</v>
       </c>
-      <c r="S7" s="8">
-        <f t="shared" si="0"/>
+      <c r="S7" s="11">
+        <f t="shared" si="2"/>
         <v>1.1859999999999999</v>
       </c>
     </row>
@@ -948,7 +1062,7 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>2.1720000000000002</v>
       </c>
       <c r="I8">
@@ -964,16 +1078,17 @@
         <v>0.97</v>
       </c>
       <c r="O8" s="6"/>
+      <c r="P8" s="12"/>
       <c r="Q8">
-        <f>SUM(I8,J8)</f>
+        <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
       <c r="R8" s="3">
-        <f>SUM(K8,L8)</f>
+        <f t="shared" si="1"/>
         <v>1.1859999999999999</v>
       </c>
-      <c r="S8" s="8">
-        <f t="shared" si="0"/>
+      <c r="S8" s="9">
+        <f t="shared" si="2"/>
         <v>1.1795</v>
       </c>
     </row>
@@ -990,7 +1105,7 @@
       <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="3">
         <v>2.0609999999999999</v>
       </c>
       <c r="I9">
@@ -1006,16 +1121,17 @@
         <v>0.97</v>
       </c>
       <c r="O9" s="6"/>
+      <c r="P9" s="12"/>
       <c r="Q9">
-        <f>SUM(I9,J9)</f>
+        <f t="shared" si="0"/>
         <v>1.1759999999999999</v>
       </c>
       <c r="R9" s="3">
-        <f>SUM(K9,L9)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S9" s="8">
-        <f t="shared" si="0"/>
+      <c r="S9" s="9">
+        <f t="shared" si="2"/>
         <v>1.1815</v>
       </c>
     </row>
@@ -1048,16 +1164,17 @@
         <v>0.97</v>
       </c>
       <c r="O10" s="6"/>
+      <c r="P10" s="12"/>
       <c r="Q10">
-        <f>SUM(I10,J10)</f>
+        <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
       <c r="R10" s="3">
-        <f>SUM(K10,L10)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S10" s="8">
-        <f t="shared" si="0"/>
+      <c r="S10" s="9">
+        <f t="shared" si="2"/>
         <v>1.1800000000000002</v>
       </c>
     </row>
@@ -1090,16 +1207,17 @@
         <v>0.96799999999999997</v>
       </c>
       <c r="O11" s="6"/>
+      <c r="P11" s="12"/>
       <c r="Q11">
-        <f>SUM(I11,J11)</f>
+        <f t="shared" si="0"/>
         <v>1.1759999999999999</v>
       </c>
       <c r="R11" s="3">
-        <f>SUM(K11,L11)</f>
+        <f t="shared" si="1"/>
         <v>1.1859999999999999</v>
       </c>
-      <c r="S11" s="8">
-        <f t="shared" si="0"/>
+      <c r="S11" s="9">
+        <f t="shared" si="2"/>
         <v>1.181</v>
       </c>
     </row>
@@ -1132,16 +1250,17 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="O12" s="6"/>
+      <c r="P12" s="12"/>
       <c r="Q12">
-        <f>SUM(I12,J12)</f>
+        <f t="shared" si="0"/>
         <v>1.177</v>
       </c>
       <c r="R12" s="3">
-        <f>SUM(K12,L12)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S12" s="8">
-        <f t="shared" si="0"/>
+      <c r="S12" s="9">
+        <f t="shared" si="2"/>
         <v>1.1819999999999999</v>
       </c>
     </row>
@@ -1158,6 +1277,10 @@
       <c r="D13" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
       <c r="I13" s="7">
         <f>AVERAGE(I7,I25,I19)</f>
         <v>0.41299999999999998</v>
@@ -1172,15 +1295,16 @@
       <c r="L13" s="8">
         <v>0.79600000000000004</v>
       </c>
-      <c r="Q13" s="3">
-        <f>SUM(I13,J13)</f>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="10">
+        <f t="shared" si="0"/>
         <v>1.1813333333333333</v>
       </c>
-      <c r="R13" s="3">
-        <f>SUM(K13,L13)</f>
+      <c r="R13" s="10">
+        <f t="shared" si="1"/>
         <v>1.1930000000000001</v>
       </c>
-      <c r="S13" s="8">
+      <c r="S13" s="11">
         <f>(Q13+R13)/2</f>
         <v>1.1871666666666667</v>
       </c>
@@ -1214,16 +1338,17 @@
         <v>0.95399999999999996</v>
       </c>
       <c r="O14" s="6"/>
+      <c r="P14" s="12"/>
       <c r="Q14">
-        <f>SUM(I14,J14)</f>
+        <f t="shared" si="0"/>
         <v>1.1759999999999999</v>
       </c>
       <c r="R14" s="3">
-        <f>SUM(K14,L14)</f>
+        <f t="shared" si="1"/>
         <v>1.177</v>
       </c>
-      <c r="S14" s="8">
-        <f t="shared" si="0"/>
+      <c r="S14" s="9">
+        <f t="shared" si="2"/>
         <v>1.1764999999999999</v>
       </c>
     </row>
@@ -1256,16 +1381,17 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="O15" s="6"/>
+      <c r="P15" s="12"/>
       <c r="Q15">
-        <f>SUM(I15,J15)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R15" s="3">
-        <f>SUM(K15,L15)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S15" s="8">
-        <f t="shared" si="0"/>
+      <c r="S15" s="9">
+        <f t="shared" si="2"/>
         <v>1.181</v>
       </c>
     </row>
@@ -1298,15 +1424,16 @@
         <v>0.99399999999999999</v>
       </c>
       <c r="O16" s="6"/>
+      <c r="P16" s="12"/>
       <c r="Q16">
-        <f>SUM(I16,J16)</f>
+        <f t="shared" si="0"/>
         <v>1.177</v>
       </c>
       <c r="R16" s="3">
-        <f>SUM(K16,L16)</f>
+        <f t="shared" si="1"/>
         <v>1.1859999999999999</v>
       </c>
-      <c r="S16" s="8">
+      <c r="S16" s="9">
         <f>(Q16+R16)/2</f>
         <v>1.1815</v>
       </c>
@@ -1340,15 +1467,16 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="O17" s="6"/>
+      <c r="P17" s="12"/>
       <c r="Q17">
-        <f>SUM(I17,J17)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R17" s="3">
-        <f>SUM(K17,L17)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S17" s="8">
+      <c r="S17" s="9">
         <f>(Q17+R17)/2</f>
         <v>1.181</v>
       </c>
@@ -1382,16 +1510,17 @@
         <v>0.96699999999999997</v>
       </c>
       <c r="O18" s="6"/>
+      <c r="P18" s="12"/>
       <c r="Q18">
-        <f>SUM(I18,J18)</f>
+        <f t="shared" si="0"/>
         <v>1.171</v>
       </c>
       <c r="R18" s="3">
-        <f>SUM(K18,L18)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="S18" s="8">
-        <f t="shared" si="0"/>
+      <c r="S18" s="9">
+        <f t="shared" si="2"/>
         <v>1.179</v>
       </c>
     </row>
@@ -1408,7 +1537,8 @@
       <c r="D19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F19" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="7">
@@ -1423,16 +1553,17 @@
       <c r="L19" s="8">
         <v>0.752</v>
       </c>
-      <c r="Q19">
-        <f>SUM(I19,J19)</f>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="4">
+        <f t="shared" si="0"/>
         <v>1.1819999999999999</v>
       </c>
-      <c r="R19" s="3">
-        <f>SUM(K19,L19)</f>
+      <c r="R19" s="10">
+        <f t="shared" si="1"/>
         <v>1.1910000000000001</v>
       </c>
-      <c r="S19" s="8">
-        <f t="shared" si="0"/>
+      <c r="S19" s="11">
+        <f t="shared" si="2"/>
         <v>1.1865000000000001</v>
       </c>
     </row>
@@ -1465,16 +1596,17 @@
         <v>0.97399999999999998</v>
       </c>
       <c r="O20" s="6"/>
+      <c r="P20" s="12"/>
       <c r="Q20">
-        <f>SUM(I20,J20)</f>
+        <f t="shared" si="0"/>
         <v>1.1759999999999999</v>
       </c>
       <c r="R20" s="3">
-        <f>SUM(K20,L20)</f>
+        <f t="shared" si="1"/>
         <v>1.1859999999999999</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.181</v>
       </c>
     </row>
@@ -1507,16 +1639,17 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="O21" s="6"/>
+      <c r="P21" s="12"/>
       <c r="Q21">
-        <f>SUM(I21,J21)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R21" s="3">
-        <f>SUM(K21,L21)</f>
+        <f t="shared" si="1"/>
         <v>1.1890000000000001</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.1819999999999999</v>
       </c>
     </row>
@@ -1525,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -1549,16 +1682,17 @@
         <v>0.97899999999999998</v>
       </c>
       <c r="O22" s="6"/>
+      <c r="P22" s="12"/>
       <c r="Q22">
-        <f>SUM(I22,J22)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R22" s="3">
-        <f>SUM(K22,L22)</f>
+        <f t="shared" si="1"/>
         <v>1.1879999999999999</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.1815</v>
       </c>
     </row>
@@ -1591,16 +1725,17 @@
         <v>0.96099999999999997</v>
       </c>
       <c r="O23" s="6"/>
+      <c r="P23" s="12"/>
       <c r="Q23">
-        <f>SUM(I23,J23)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R23" s="3">
-        <f>SUM(K23,L23)</f>
+        <f t="shared" si="1"/>
         <v>1.1879999999999999</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.1815</v>
       </c>
     </row>
@@ -1633,16 +1768,17 @@
         <v>0.97599999999999998</v>
       </c>
       <c r="O24" s="6"/>
+      <c r="P24" s="12"/>
       <c r="Q24">
-        <f>SUM(I24,J24)</f>
+        <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
       <c r="R24" s="3">
-        <f>SUM(K24,L24)</f>
+        <f t="shared" si="1"/>
         <v>1.1870000000000001</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.181</v>
       </c>
     </row>
@@ -1656,9 +1792,11 @@
       <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="14" t="s">
         <v>14</v>
       </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
       <c r="I25">
         <v>0.42599999999999999</v>
       </c>
@@ -1671,17 +1809,583 @@
       <c r="L25" s="3">
         <v>0.753</v>
       </c>
-      <c r="Q25">
-        <f>SUM(I25,J25)</f>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="4">
+        <f t="shared" si="0"/>
         <v>1.181</v>
       </c>
-      <c r="R25" s="3">
-        <f>SUM(K25,L25)</f>
+      <c r="R25" s="10">
+        <f t="shared" si="1"/>
         <v>1.194</v>
       </c>
-      <c r="S25" s="3">
-        <f t="shared" si="0"/>
+      <c r="S25" s="10">
+        <f t="shared" si="2"/>
         <v>1.1875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA76E4F-0C7E-4ED7-94CE-8D9008DC0B40}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E2" s="17">
+        <f>D2-D2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="18">
+        <f>E2*24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="17">
+        <v>0.40555555555555556</v>
+      </c>
+      <c r="E3" s="17">
+        <f>D3-$D$2</f>
+        <v>9.7222222222222432E-3</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F25" si="0">E3*24</f>
+        <v>0.23333333333333384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E4" s="17">
+        <f>D4-$D$2</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="E5" s="17">
+        <f t="shared" ref="E5:E7" si="1">D5-$D$2</f>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E6" s="17">
+        <f t="shared" si="1"/>
+        <v>5.208333333333337E-2</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>1.2500000000000009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" s="17">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="E8" s="17">
+        <f>D8-$D$2</f>
+        <v>2.0138888888888928E-2</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0.48333333333333428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E9" s="17">
+        <f>D9-$D$2</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="E10" s="17">
+        <f>D10-$D$2</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="17">
+        <f>D11-$D$2</f>
+        <v>0.10416666666666669</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>2.5000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E12" s="17">
+        <f>D12-$D$2</f>
+        <v>0.11458333333333331</v>
+      </c>
+      <c r="F12" s="18">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E13" s="17">
+        <f>D13-$D$2</f>
+        <v>0.12500000000000006</v>
+      </c>
+      <c r="F13" s="18">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>11</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E14" s="17">
+        <f>D14-$D$2</f>
+        <v>0.14583333333333331</v>
+      </c>
+      <c r="F14" s="18">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E15" s="17">
+        <f>D15-$D$2</f>
+        <v>0.15625000000000006</v>
+      </c>
+      <c r="F15" s="18">
+        <f t="shared" si="0"/>
+        <v>3.7500000000000013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="E16" s="17">
+        <f>D16-$D$2</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="F16" s="18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="E17" s="17">
+        <f>D17-$D$2</f>
+        <v>0.17708333333333331</v>
+      </c>
+      <c r="F17" s="18">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>21</v>
+      </c>
+      <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E18" s="17">
+        <f>D18-$D$2</f>
+        <v>0.18750000000000006</v>
+      </c>
+      <c r="F18" s="18">
+        <f t="shared" si="0"/>
+        <v>4.5000000000000018</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.59375</v>
+      </c>
+      <c r="E19" s="17">
+        <f>D19-$D$2</f>
+        <v>0.19791666666666669</v>
+      </c>
+      <c r="F19" s="18">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="E20" s="17">
+        <f>D20-$D$2</f>
+        <v>0.21875000000000006</v>
+      </c>
+      <c r="F20" s="18">
+        <f t="shared" si="0"/>
+        <v>5.2500000000000018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>17</v>
+      </c>
+      <c r="D21" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E21" s="17">
+        <f>D21-$D$2</f>
+        <v>0.22916666666666669</v>
+      </c>
+      <c r="F21" s="18">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>24</v>
+      </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
+      <c r="D22" s="17">
+        <v>0.63541666666666696</v>
+      </c>
+      <c r="E22" s="17">
+        <f>D22-$D$2</f>
+        <v>0.23958333333333365</v>
+      </c>
+      <c r="F22" s="18">
+        <f t="shared" si="0"/>
+        <v>5.7500000000000071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>19</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="17">
+        <f>D23-$D$2</f>
+        <v>0.24999999999999972</v>
+      </c>
+      <c r="F23" s="18">
+        <f t="shared" si="0"/>
+        <v>5.9999999999999929</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24" s="17">
+        <v>0.65625</v>
+      </c>
+      <c r="E24" s="17">
+        <f>D24-$D$2</f>
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="F24" s="18">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E25" s="17">
+        <f>D25-$D$2</f>
+        <v>0.27083333333333365</v>
+      </c>
+      <c r="F25" s="18">
+        <f t="shared" si="0"/>
+        <v>6.5000000000000071</v>
       </c>
     </row>
   </sheetData>
